--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486761_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486761_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722</v>
+        <v>0.121</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4708</v>
+        <v>-0.0502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.643</v>
+        <v>0.1712</v>
       </c>
       <c r="G2" t="n">
         <v>-5.2532</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1823</v>
+        <v>0.1312</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7451</v>
+        <v>-0.3245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9275</v>
+        <v>0.4557</v>
       </c>
       <c r="V2" t="n">
         <v>3.3122</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6247</v>
+        <v>-0.004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2758</v>
+        <v>0.6482</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9005</v>
+        <v>-0.6522</v>
       </c>
       <c r="G3" t="n">
         <v>0.1716</v>
@@ -688,13 +688,13 @@
         <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4415</v>
+        <v>0.1793</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5244</v>
+        <v>-0.152</v>
       </c>
       <c r="U3" t="n">
-        <v>0.083</v>
+        <v>0.3313</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5133</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8031</v>
+        <v>-0.8803</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5072</v>
+        <v>1.3555</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3102</v>
+        <v>-2.2357</v>
       </c>
       <c r="G4" t="n">
         <v>1.457</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3366</v>
+        <v>-0.4138</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0832</v>
+        <v>-0.2349</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2534</v>
+        <v>-0.1789</v>
       </c>
       <c r="V4" t="n">
         <v>0.2004</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.468</v>
+        <v>-1.8929</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.71</v>
+        <v>-3.6022</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.758</v>
+        <v>1.7093</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1657</v>
+        <v>-0.2367</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0415</v>
+        <v>-0.7588</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2072</v>
+        <v>0.5221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3178</v>
+        <v>0.2196</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3178</v>
+        <v>0.1382</v>
       </c>
       <c r="L5" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.4563</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.897</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-2.1239</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-3.8616</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.7377</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-1.4835</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.2763</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1.2072</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.5792</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5446</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9873</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5788</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.4085</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2.8689</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1.6412</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.497</v>
+        <v>-3.2554</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.1815</v>
+        <v>-2.3236</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6845</v>
+        <v>-0.9319</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2367</v>
+        <v>-1.1657</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7588</v>
+        <v>0.0415</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5221</v>
+        <v>-1.2072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2196</v>
+        <v>0.3178</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1382</v>
+        <v>0.3178</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4563</v>
+        <v>-1.4835</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.897</v>
+        <v>-0.2763</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4408</v>
+        <v>-1.2072</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1239</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4969</v>
+        <v>-0.0348</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4031</v>
+        <v>0.2347</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0426</v>
+        <v>-2.8689</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0426</v>
+        <v>-1.6412</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.178</v>
+        <v>-4.0042</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5661</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6119</v>
+        <v>-3.4381</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0152</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2633</v>
+        <v>-1.0895</v>
       </c>
       <c r="T7" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6011</v>
+        <v>-0.4273</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.4326</v>
+        <v>-5.8327</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9666</v>
+        <v>-4.5414</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.466</v>
+        <v>-1.2913</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4577</v>
+        <v>-6.7439</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.255</v>
+        <v>-0.6696</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2028</v>
+        <v>-6.0744</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5807</v>
+        <v>-3.2455</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7028</v>
+        <v>0.1589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>-3.4044</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.877</v>
+        <v>-3.4984</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5522</v>
+        <v>-0.8285</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3248</v>
+        <v>-2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.8616</v>
+        <v>-3.6685</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.827</v>
+        <v>-5.7923</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4579</v>
+        <v>-0.331</v>
       </c>
       <c r="T8" t="n">
-        <v>0.441</v>
+        <v>-0.4143</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0169</v>
+        <v>0.0833</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5712</v>
+        <v>4.9108</v>
       </c>
       <c r="W8" t="n">
+        <v>4.9108</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.5712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.5112</v>
+        <v>-6.7663</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1206</v>
+        <v>-5.3252</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3906</v>
+        <v>-1.4411</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.7439</v>
+        <v>-2.4577</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6696</v>
+        <v>-1.255</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.0744</v>
+        <v>-1.2028</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.2455</v>
+        <v>-0.5807</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1589</v>
+        <v>-0.7028</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.4044</v>
+        <v>0.1221</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4984</v>
+        <v>-1.877</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8285</v>
+        <v>-0.5522</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.67</v>
+        <v>-1.3248</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.6685</v>
+        <v>-3.8616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7923</v>
+        <v>-4.827</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0095</v>
+        <v>0.1242</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9935</v>
+        <v>0.0825</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.016</v>
+        <v>0.0417</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9108</v>
+        <v>-0.5712</v>
       </c>
       <c r="W9" t="n">
-        <v>4.9108</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-23.3424</v>
+        <v>-22.5148</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.2326</v>
+        <v>-14.405</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.1097</v>
+        <v>-8.1098</v>
       </c>
       <c r="G10" t="n">
         <v>-17.2438</v>
@@ -1207,7 +1207,7 @@
         <v>-16.2092</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4412000000000003</v>
+        <v>-0.4412000000000007</v>
       </c>
       <c r="K10" t="n">
         <v>3.1077</v>
@@ -1225,7 +1225,7 @@
         <v>-12.6602</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.723199999999999</v>
+        <v>-7.7232</v>
       </c>
       <c r="Q10" t="n">
         <v>-20.2733</v>
@@ -1234,16 +1234,16 @@
         <v>12.5502</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5172</v>
+        <v>-0.6894</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.4855</v>
+        <v>-1.6578</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9685</v>
+        <v>0.9684</v>
       </c>
       <c r="V10" t="n">
-        <v>3.1418</v>
+        <v>3.141799999999999</v>
       </c>
       <c r="W10" t="n">
         <v>7.9673</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.030900000000001</v>
+        <v>9.210100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>5.8114</v>
+        <v>6.3285</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2195</v>
+        <v>2.8815</v>
       </c>
       <c r="G11" t="n">
         <v>7.3176</v>
@@ -1312,13 +1312,13 @@
         <v>3.2823</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1861</v>
+        <v>-0.007</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8554</v>
+        <v>-0.3383</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3307</v>
+        <v>0.3313</v>
       </c>
       <c r="V11" t="n">
         <v>1.5133</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1329</v>
+        <v>6.144</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6817</v>
+        <v>1.268</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4513</v>
+        <v>4.876</v>
       </c>
       <c r="G12" t="n">
         <v>2.2783</v>
@@ -1390,13 +1390,13 @@
         <v>3.2823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5956</v>
+        <v>0.6067</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5788</v>
+        <v>0.1651</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0169</v>
+        <v>0.4416</v>
       </c>
       <c r="V12" t="n">
         <v>0.9421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6003</v>
+        <v>5.567</v>
       </c>
       <c r="E13" t="n">
         <v>2.4329</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1674</v>
+        <v>3.1341</v>
       </c>
       <c r="G13" t="n">
         <v>4.3356</v>
@@ -1468,13 +1468,13 @@
         <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9711</v>
+        <v>0.9378</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1659</v>
       </c>
       <c r="U13" t="n">
-        <v>1.137</v>
+        <v>1.1037</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2856</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.236</v>
+        <v>5.0745</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5018</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6308</v>
+        <v>4.5726</v>
       </c>
       <c r="G14" t="n">
         <v>0.6637</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1202</v>
+        <v>0.9587</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0272</v>
+        <v>-0.0762</v>
       </c>
       <c r="U14" t="n">
-        <v>1.093</v>
+        <v>1.0349</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6181</v>
+        <v>1.9588</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2892</v>
+        <v>1.3927</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3289</v>
+        <v>0.5661</v>
       </c>
       <c r="G15" t="n">
         <v>2.7202</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4303</v>
+        <v>-0.0897</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1767</v>
+        <v>0.4139</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.312</v>
+        <v>0.1574</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-1.1408</v>
       </c>
       <c r="F16" t="n">
-        <v>1.246</v>
+        <v>1.2983</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7894</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5407</v>
+        <v>0.3862</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2756</v>
+        <v>0.0687</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2652</v>
+        <v>0.3175</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7563</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6564</v>
+        <v>-0.1185</v>
       </c>
       <c r="E17" t="n">
         <v>-4.0663</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4099</v>
+        <v>3.9477</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6396</v>
@@ -1780,13 +1780,13 @@
         <v>3.0892</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1103</v>
+        <v>0.6482</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1384</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2487</v>
+        <v>0.7865</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6785</v>
+        <v>-0.4107</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1469</v>
+        <v>0.0796</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5316</v>
+        <v>-0.4903</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3953</v>
+        <v>1.4928</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5241</v>
+        <v>-0.214</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1288</v>
+        <v>1.7068</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5053</v>
+        <v>2.1071</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6274</v>
+        <v>0.6828</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1221</v>
+        <v>1.4242</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8899</v>
+        <v>-0.6143</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.8969</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0068</v>
+        <v>0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3805</v>
+        <v>0.2896</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3584</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0221</v>
+        <v>0.3863</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.243</v>
+        <v>-1.2277</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.243</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>E. QUIJADA GARCÍA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0038</v>
+        <v>-0.7058</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1273</v>
+        <v>1.7706</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-2.4763</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4928</v>
+        <v>2.2599</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.214</v>
+        <v>0.9103</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7068</v>
+        <v>1.3496</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1071</v>
+        <v>2.6671</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6828</v>
+        <v>1.3243</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4242</v>
+        <v>1.3428</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6143</v>
+        <v>-0.4072</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8969</v>
+        <v>-0.414</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2826</v>
+        <v>0.0068</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.7723</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3034</v>
+        <v>0.262</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3036</v>
+        <v>0.0688</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0001</v>
+        <v>0.1932</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2277</v>
+        <v>-2.4554</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2277</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. QUIJADA GARCÍA</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2491</v>
+        <v>-0.7764</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5637</v>
+        <v>-0.4572</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8129</v>
+        <v>-0.3192</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2599</v>
+        <v>-1.3953</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9103</v>
+        <v>-1.5241</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3496</v>
+        <v>0.1288</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6671</v>
+        <v>-0.5053</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3243</v>
+        <v>-0.6274</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3428</v>
+        <v>0.1221</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4072</v>
+        <v>-0.8899</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.414</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0.0068</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2814</v>
+        <v>0.2826</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.138</v>
+        <v>0.0481</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1434</v>
+        <v>0.2345</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4554</v>
+        <v>-0.243</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4554</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>23.3424</v>
+        <v>26.1004</v>
       </c>
       <c r="E21" t="n">
-        <v>8.1097</v>
+        <v>8.1098</v>
       </c>
       <c r="F21" t="n">
-        <v>15.2328</v>
+        <v>17.9905</v>
       </c>
       <c r="G21" t="n">
         <v>17.2438</v>
@@ -2083,7 +2083,7 @@
         <v>3.549</v>
       </c>
       <c r="P21" t="n">
-        <v>7.722999999999999</v>
+        <v>7.723000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-12.5502</v>
@@ -2092,13 +2092,13 @@
         <v>20.273</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5172</v>
+        <v>4.2751</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9683</v>
+        <v>-0.9684000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4856</v>
+        <v>5.243399999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-3.1417</v>
